--- a/docs/testing/PROJECT TEST CASES CAA 261026.xlsx
+++ b/docs/testing/PROJECT TEST CASES CAA 261026.xlsx
@@ -3150,7 +3150,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>E02-S05 - Scenario 1 (Previous event copied; assumes O-51)</t>
+          <t>E02-S05 - Scenario 1 (Previous event copied; T-99)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -15005,25 +15005,25 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Event "Community Meetup" is open for registration</t>
+          <t>Event "Community Meetup" is open for registration; attendee_e@example.com's account has no contact number. Registration details are the account's name, email address and contact number, so nothing extra is entered at registration (T-32, O-05); every account has an email, so the contact number is the detail that can be missing.</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_e@example.com
   2. Open event "Community Meetup"
-  3. Leave the Email field empty
+  3. Open registration, select a Session and review the details shown from the account
   4. Submit registration</t>
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>Name: filled | Email: (blank)</t>
+          <t>Name: from account | Email: from account | Contact number: (blank on the account)</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>Registration is blocked, and the Email field is identified as missing</t>
+          <t>Registration is blocked, and Contact number is identified as missing, with a link to add it on the Profile page; no registration is created</t>
         </is>
       </c>
     </row>
@@ -15347,7 +15347,7 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>E09-S02 - Scenario 5 (Waiting list remains event-level; assumes O-50)</t>
+          <t>E09-S02 - Scenario 5 (Waiting list remains event-level; T-98)</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>E09-S02 - Scenario 2 (Over-capacity submission remains Pending); assumes O-50</t>
+          <t>E09-S02 - Scenario 2 (Over-capacity submission remains Pending); T-98</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
@@ -15591,7 +15591,7 @@
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>The request is saved as Pending for Organiser review; it does not consume an approved seat or create a Session waitlist (assumes O-50)</t>
+          <t>The request is saved as Pending for Organiser review; it does not consume an approved seat or create a Session waitlist (T-98)</t>
         </is>
       </c>
     </row>
@@ -16226,7 +16226,7 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>E09-S04 - Scenario 1 (Joined a full Event's list); assumes O-50</t>
+          <t>E09-S04 - Scenario 1 (Joined a full Event's list); T-98</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>attendee_i@example.com is added to the Event-level waiting list and receives confirmation; no Session-specific waiting-list entry is created (assumes O-50)</t>
+          <t>attendee_i@example.com is added to the Event-level waiting list and receives confirmation; no Session-specific waiting-list entry is created (T-98)</t>
         </is>
       </c>
     </row>
